--- a/frontend/public/DFW_HVAC_Site_Audit.xlsx
+++ b/frontend/public/DFW_HVAC_Site_Audit.xlsx
@@ -540,7 +540,7 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>CMS Navigation</t>
+          <t>Live URL</t>
         </is>
       </c>
     </row>
@@ -572,7 +572,7 @@
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>Sanity &gt; Homepage &gt; metaTitle / metaDescription</t>
+          <t>https://dfwhvac.com/</t>
         </is>
       </c>
     </row>
@@ -594,7 +594,7 @@
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>Sanity &gt; About Page &gt; metaTitle / metaDescription</t>
+          <t>https://dfwhvac.com/about</t>
         </is>
       </c>
     </row>
@@ -616,7 +616,7 @@
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>Sanity &gt; Contact Page &gt; metaTitle / metaDescription</t>
+          <t>https://dfwhvac.com/contact</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>Hardcoded in code (app/services/page.jsx)</t>
+          <t>https://dfwhvac.com/services</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>Sanity &gt; FAQ Page &gt; metaDescription</t>
+          <t>https://dfwhvac.com/faq</t>
         </is>
       </c>
     </row>
@@ -682,7 +682,7 @@
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>Sanity &gt; Reviews Page &gt; metaDescription</t>
+          <t>https://dfwhvac.com/reviews</t>
         </is>
       </c>
     </row>
@@ -704,7 +704,7 @@
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>Hardcoded in code (app/request-service/page.jsx)</t>
+          <t>https://dfwhvac.com/request-service</t>
         </is>
       </c>
     </row>
@@ -726,7 +726,7 @@
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>Hardcoded in code (app/estimate/page.jsx)</t>
+          <t>https://dfwhvac.com/estimate</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>Hardcoded in code (app/cities-served/page.jsx)</t>
+          <t>https://dfwhvac.com/cities-served</t>
         </is>
       </c>
     </row>
@@ -770,7 +770,7 @@
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>Hardcoded in code (app/privacy-policy/page.jsx)</t>
+          <t>https://dfwhvac.com/privacy-policy</t>
         </is>
       </c>
     </row>
@@ -792,7 +792,7 @@
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>Hardcoded in code (app/terms-of-service/page.jsx)</t>
+          <t>https://dfwhvac.com/terms-of-service</t>
         </is>
       </c>
     </row>
@@ -814,7 +814,7 @@
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>N/A - will become Showcase Projects page</t>
+          <t>https://dfwhvac.com/recent-projects</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>Sanity &gt; Service &gt; Air Conditioning &gt; metaTitle / metaDescription</t>
+          <t>https://dfwhvac.com/services/residential/air-conditioning</t>
         </is>
       </c>
     </row>
@@ -868,7 +868,7 @@
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>Sanity &gt; Service &gt; Heating &gt; metaTitle / metaDescription</t>
+          <t>https://dfwhvac.com/services/residential/heating</t>
         </is>
       </c>
     </row>
@@ -890,7 +890,7 @@
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>Sanity &gt; Service &gt; Preventative Maintenance &gt; metaTitle / metaDescription</t>
+          <t>https://dfwhvac.com/services/residential/preventative-maintenance</t>
         </is>
       </c>
     </row>
@@ -912,7 +912,7 @@
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>Sanity &gt; Service &gt; Indoor Air Quality &gt; metaTitle / metaDescription</t>
+          <t>https://dfwhvac.com/services/residential/indoor-air-quality</t>
         </is>
       </c>
     </row>
@@ -934,7 +934,7 @@
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>Sanity &gt; Service &gt; Commercial Air Conditioning &gt; metaTitle / metaDescription</t>
+          <t>https://dfwhvac.com/services/commercial/commercial-air-conditioning</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>Sanity &gt; Service &gt; Commercial Heating &gt; metaTitle / metaDescription</t>
+          <t>https://dfwhvac.com/services/commercial/commercial-heating</t>
         </is>
       </c>
     </row>
@@ -978,7 +978,7 @@
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>Sanity &gt; Service &gt; Commercial Maintenance &gt; metaTitle / metaDescription</t>
+          <t>https://dfwhvac.com/services/commercial/commercial-maintenance</t>
         </is>
       </c>
     </row>
@@ -1010,7 +1010,7 @@
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>Sanity &gt; City Page &gt; allen</t>
+          <t>https://dfwhvac.com/cities-served/allen</t>
         </is>
       </c>
     </row>
@@ -1032,7 +1032,7 @@
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>Sanity &gt; City Page &gt; argyle</t>
+          <t>https://dfwhvac.com/cities-served/argyle</t>
         </is>
       </c>
     </row>
@@ -1054,7 +1054,7 @@
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>Sanity &gt; City Page &gt; arlington</t>
+          <t>https://dfwhvac.com/cities-served/arlington</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>Sanity &gt; City Page &gt; bedford</t>
+          <t>https://dfwhvac.com/cities-served/bedford</t>
         </is>
       </c>
     </row>
@@ -1098,7 +1098,7 @@
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>Sanity &gt; City Page &gt; carrollton</t>
+          <t>https://dfwhvac.com/cities-served/carrollton</t>
         </is>
       </c>
     </row>
@@ -1120,7 +1120,7 @@
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>Sanity &gt; City Page &gt; colleyville</t>
+          <t>https://dfwhvac.com/cities-served/colleyville</t>
         </is>
       </c>
     </row>
@@ -1142,7 +1142,7 @@
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>Sanity &gt; City Page &gt; coppell</t>
+          <t>https://dfwhvac.com/cities-served/coppell</t>
         </is>
       </c>
     </row>
@@ -1164,7 +1164,7 @@
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>Sanity &gt; City Page &gt; dallas</t>
+          <t>https://dfwhvac.com/cities-served/dallas</t>
         </is>
       </c>
     </row>
@@ -1186,7 +1186,7 @@
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>Sanity &gt; City Page &gt; denton</t>
+          <t>https://dfwhvac.com/cities-served/denton</t>
         </is>
       </c>
     </row>
@@ -1208,7 +1208,7 @@
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>Sanity &gt; City Page &gt; euless</t>
+          <t>https://dfwhvac.com/cities-served/euless</t>
         </is>
       </c>
     </row>
@@ -1230,7 +1230,7 @@
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>Sanity &gt; City Page &gt; farmers-branch</t>
+          <t>https://dfwhvac.com/cities-served/farmers-branch</t>
         </is>
       </c>
     </row>
@@ -1252,7 +1252,7 @@
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>Sanity &gt; City Page &gt; flower-mound</t>
+          <t>https://dfwhvac.com/cities-served/flower-mound</t>
         </is>
       </c>
     </row>
@@ -1274,7 +1274,7 @@
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>Sanity &gt; City Page &gt; fort-worth</t>
+          <t>https://dfwhvac.com/cities-served/fort-worth</t>
         </is>
       </c>
     </row>
@@ -1296,7 +1296,7 @@
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>Sanity &gt; City Page &gt; frisco</t>
+          <t>https://dfwhvac.com/cities-served/frisco</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>Sanity &gt; City Page &gt; grapevine</t>
+          <t>https://dfwhvac.com/cities-served/grapevine</t>
         </is>
       </c>
     </row>
@@ -1340,7 +1340,7 @@
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>Sanity &gt; City Page &gt; haslet</t>
+          <t>https://dfwhvac.com/cities-served/haslet</t>
         </is>
       </c>
     </row>
@@ -1362,7 +1362,7 @@
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>Sanity &gt; City Page &gt; hurst</t>
+          <t>https://dfwhvac.com/cities-served/hurst</t>
         </is>
       </c>
     </row>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>Sanity &gt; City Page &gt; irving</t>
+          <t>https://dfwhvac.com/cities-served/irving</t>
         </is>
       </c>
     </row>
@@ -1406,7 +1406,7 @@
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>Sanity &gt; City Page &gt; keller</t>
+          <t>https://dfwhvac.com/cities-served/keller</t>
         </is>
       </c>
     </row>
@@ -1428,7 +1428,7 @@
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>Sanity &gt; City Page &gt; lake-dallas</t>
+          <t>https://dfwhvac.com/cities-served/lake-dallas</t>
         </is>
       </c>
     </row>
@@ -1450,7 +1450,7 @@
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>Sanity &gt; City Page &gt; lewisville</t>
+          <t>https://dfwhvac.com/cities-served/lewisville</t>
         </is>
       </c>
     </row>
@@ -1472,7 +1472,7 @@
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>Sanity &gt; City Page &gt; mansfield</t>
+          <t>https://dfwhvac.com/cities-served/mansfield</t>
         </is>
       </c>
     </row>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>Sanity &gt; City Page &gt; north-richland-hills</t>
+          <t>https://dfwhvac.com/cities-served/north-richland-hills</t>
         </is>
       </c>
     </row>
@@ -1516,7 +1516,7 @@
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>Sanity &gt; City Page &gt; plano</t>
+          <t>https://dfwhvac.com/cities-served/plano</t>
         </is>
       </c>
     </row>
@@ -1538,7 +1538,7 @@
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>Sanity &gt; City Page &gt; richardson</t>
+          <t>https://dfwhvac.com/cities-served/richardson</t>
         </is>
       </c>
     </row>
@@ -1560,7 +1560,7 @@
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>Sanity &gt; City Page &gt; roanoke</t>
+          <t>https://dfwhvac.com/cities-served/roanoke</t>
         </is>
       </c>
     </row>
@@ -1582,7 +1582,7 @@
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>Sanity &gt; City Page &gt; southlake</t>
+          <t>https://dfwhvac.com/cities-served/southlake</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t>Sanity &gt; City Page &gt; the-colony</t>
+          <t>https://dfwhvac.com/cities-served/the-colony</t>
         </is>
       </c>
     </row>

--- a/frontend/public/DFW_HVAC_Site_Audit.xlsx
+++ b/frontend/public/DFW_HVAC_Site_Audit.xlsx
@@ -836,7 +836,7 @@
       </c>
       <c r="B16" s="9" t="inlineStr">
         <is>
-          <t>(null - using code fallback)</t>
+          <t>FALLBACK: Complete AC installation, repair, and replacement services for Dallas-Fort Worth homes.</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
@@ -858,7 +858,7 @@
       </c>
       <c r="B17" s="9" t="inlineStr">
         <is>
-          <t>(null - using code fallback)</t>
+          <t>FALLBACK: Furnace repair, heat pump service, and heating system installation for DFW homes.</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="B18" s="9" t="inlineStr">
         <is>
-          <t>(null - using code fallback)</t>
+          <t>FALLBACK: Regular maintenance to keep your HVAC system running efficiently year-round.</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
@@ -902,7 +902,7 @@
       </c>
       <c r="B19" s="9" t="inlineStr">
         <is>
-          <t>(null - using code fallback)</t>
+          <t>FALLBACK: Improve your home's air quality with our specialized solutions.</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
@@ -924,7 +924,7 @@
       </c>
       <c r="B20" s="9" t="inlineStr">
         <is>
-          <t>(null - using code fallback)</t>
+          <t>FALLBACK: Large-scale AC systems for businesses and commercial properties in the DFW area.</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
@@ -946,7 +946,7 @@
       </c>
       <c r="B21" s="9" t="inlineStr">
         <is>
-          <t>(null - using code fallback)</t>
+          <t>FALLBACK: Commercial heating solutions and repair to keep businesses and commercial properties comfortable.</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
@@ -968,7 +968,7 @@
       </c>
       <c r="B22" s="9" t="inlineStr">
         <is>
-          <t>(null - using code fallback)</t>
+          <t>FALLBACK: Comprehensive maintenance programs that help businesses keep their HVAC systems running efficiently and avoid downtime.</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
@@ -1000,7 +1000,7 @@
       </c>
       <c r="B24" s="9" t="inlineStr">
         <is>
-          <t>(null - using code fallback)</t>
+          <t>FALLBACK: Professional heating and air conditioning services in Allen, Texas. Same-day HVAC repair, installation, and maintenance. Serving zip codes: 75013.</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
@@ -1022,7 +1022,7 @@
       </c>
       <c r="B25" s="9" t="inlineStr">
         <is>
-          <t>(null - using code fallback)</t>
+          <t>FALLBACK: Professional heating and air conditioning services in Argyle, Texas. Same-day HVAC repair, installation, and maintenance. Serving zip codes: 76226.</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
@@ -1044,7 +1044,7 @@
       </c>
       <c r="B26" s="9" t="inlineStr">
         <is>
-          <t>(null - using code fallback)</t>
+          <t>FALLBACK: Professional heating and air conditioning services in Arlington, Texas. Same-day HVAC repair, installation, and maintenance. Serving zip codes: 76001, 76002, 76012, 76013, 76014, 76015, 76016, 76017, 76018.</t>
         </is>
       </c>
       <c r="C26" s="6" t="inlineStr">
@@ -1066,7 +1066,7 @@
       </c>
       <c r="B27" s="9" t="inlineStr">
         <is>
-          <t>(null - using code fallback)</t>
+          <t>FALLBACK: Professional heating and air conditioning services in Bedford, Texas. Same-day HVAC repair, installation, and maintenance. Serving zip codes: 76021, 76022.</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
@@ -1088,7 +1088,7 @@
       </c>
       <c r="B28" s="9" t="inlineStr">
         <is>
-          <t>(null - using code fallback)</t>
+          <t>FALLBACK: Professional heating and air conditioning services in Carrollton, Texas. Same-day HVAC repair, installation, and maintenance. Serving zip codes: 75006, 75007, 75010.</t>
         </is>
       </c>
       <c r="C28" s="6" t="inlineStr">
@@ -1110,7 +1110,7 @@
       </c>
       <c r="B29" s="9" t="inlineStr">
         <is>
-          <t>(null - using code fallback)</t>
+          <t>FALLBACK: Professional heating and air conditioning services in Colleyville, Texas. Same-day HVAC repair, installation, and maintenance. Serving zip codes: 76034.</t>
         </is>
       </c>
       <c r="C29" s="6" t="inlineStr">
@@ -1132,7 +1132,7 @@
       </c>
       <c r="B30" s="9" t="inlineStr">
         <is>
-          <t>(null - using code fallback)</t>
+          <t>FALLBACK: Professional heating and air conditioning services in Coppell, Texas. Same-day HVAC repair, installation, and maintenance. Serving zip codes: 75019.</t>
         </is>
       </c>
       <c r="C30" s="6" t="inlineStr">
@@ -1154,7 +1154,7 @@
       </c>
       <c r="B31" s="9" t="inlineStr">
         <is>
-          <t>(null - using code fallback)</t>
+          <t>FALLBACK: Professional heating and air conditioning services in Dallas, Texas. Same-day HVAC repair, installation, and maintenance. Serving zip codes: 75201, 75202, 75204, 75205, 75206, 75207, 75208, 75209, 75214, 75218, 75219, 75225, 75229, 75230, 75238, 75244, 75248, 75254.</t>
         </is>
       </c>
       <c r="C31" s="6" t="inlineStr">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="B32" s="9" t="inlineStr">
         <is>
-          <t>(null - using code fallback)</t>
+          <t>FALLBACK: Professional heating and air conditioning services in Denton, Texas. Same-day HVAC repair, installation, and maintenance. Serving zip codes: 76210.</t>
         </is>
       </c>
       <c r="C32" s="6" t="inlineStr">
@@ -1198,7 +1198,7 @@
       </c>
       <c r="B33" s="9" t="inlineStr">
         <is>
-          <t>(null - using code fallback)</t>
+          <t>FALLBACK: Professional heating and air conditioning services in Euless, Texas. Same-day HVAC repair, installation, and maintenance. Serving zip codes: 76039, 76040.</t>
         </is>
       </c>
       <c r="C33" s="6" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="B34" s="9" t="inlineStr">
         <is>
-          <t>(null - using code fallback)</t>
+          <t>FALLBACK: Professional heating and air conditioning services in Farmers Branch, Texas. Same-day HVAC repair, installation, and maintenance. Serving zip codes: 75234.</t>
         </is>
       </c>
       <c r="C34" s="6" t="inlineStr">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="B35" s="9" t="inlineStr">
         <is>
-          <t>(null - using code fallback)</t>
+          <t>FALLBACK: Professional heating and air conditioning services in Flower Mound, Texas. Same-day HVAC repair, installation, and maintenance. Serving zip codes: 75022, 75028, 75077.</t>
         </is>
       </c>
       <c r="C35" s="6" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="B36" s="9" t="inlineStr">
         <is>
-          <t>(null - using code fallback)</t>
+          <t>FALLBACK: Professional heating and air conditioning services in Fort Worth, Texas. Same-day HVAC repair, installation, and maintenance. Serving zip codes: 76118, 76120, 76137, 76177.</t>
         </is>
       </c>
       <c r="C36" s="6" t="inlineStr">
@@ -1286,7 +1286,7 @@
       </c>
       <c r="B37" s="9" t="inlineStr">
         <is>
-          <t>(null - using code fallback)</t>
+          <t>FALLBACK: Professional heating and air conditioning services in Frisco, Texas. Same-day HVAC repair, installation, and maintenance. Serving zip codes: 75033, 75034, 75035, 75036.</t>
         </is>
       </c>
       <c r="C37" s="6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="B38" s="9" t="inlineStr">
         <is>
-          <t>(null - using code fallback)</t>
+          <t>FALLBACK: Professional heating and air conditioning services in Grapevine, Texas. Same-day HVAC repair, installation, and maintenance. Serving zip codes: 76051.</t>
         </is>
       </c>
       <c r="C38" s="6" t="inlineStr">
@@ -1330,7 +1330,7 @@
       </c>
       <c r="B39" s="9" t="inlineStr">
         <is>
-          <t>(null - using code fallback)</t>
+          <t>FALLBACK: Professional heating and air conditioning services in Haslet, Texas. Same-day HVAC repair, installation, and maintenance. Serving zip codes: 76052.</t>
         </is>
       </c>
       <c r="C39" s="6" t="inlineStr">
@@ -1352,7 +1352,7 @@
       </c>
       <c r="B40" s="9" t="inlineStr">
         <is>
-          <t>(null - using code fallback)</t>
+          <t>FALLBACK: Professional heating and air conditioning services in Hurst, Texas. Same-day HVAC repair, installation, and maintenance. Serving zip codes: 76054.</t>
         </is>
       </c>
       <c r="C40" s="6" t="inlineStr">
@@ -1374,7 +1374,7 @@
       </c>
       <c r="B41" s="9" t="inlineStr">
         <is>
-          <t>(null - using code fallback)</t>
+          <t>FALLBACK: Professional heating and air conditioning services in Irving, Texas. Same-day HVAC repair, installation, and maintenance. Serving zip codes: 75038, 75039, 75062, 75063.</t>
         </is>
       </c>
       <c r="C41" s="6" t="inlineStr">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="B42" s="9" t="inlineStr">
         <is>
-          <t>(null - using code fallback)</t>
+          <t>FALLBACK: Professional heating and air conditioning services in Keller, Texas. Same-day HVAC repair, installation, and maintenance. Serving zip codes: 76244, 76248.</t>
         </is>
       </c>
       <c r="C42" s="6" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="B43" s="9" t="inlineStr">
         <is>
-          <t>(null - using code fallback)</t>
+          <t>FALLBACK: Professional heating and air conditioning services in Lake Dallas, Texas. Same-day HVAC repair, installation, and maintenance. Serving zip codes: 75065.</t>
         </is>
       </c>
       <c r="C43" s="6" t="inlineStr">
@@ -1440,7 +1440,7 @@
       </c>
       <c r="B44" s="9" t="inlineStr">
         <is>
-          <t>(null - using code fallback)</t>
+          <t>FALLBACK: Professional heating and air conditioning services in Lewisville, Texas. Same-day HVAC repair, installation, and maintenance. Serving zip codes: 75057, 75067.</t>
         </is>
       </c>
       <c r="C44" s="6" t="inlineStr">
@@ -1462,7 +1462,7 @@
       </c>
       <c r="B45" s="9" t="inlineStr">
         <is>
-          <t>(null - using code fallback)</t>
+          <t>FALLBACK: Professional heating and air conditioning services in Mansfield, Texas. Same-day HVAC repair, installation, and maintenance. Serving zip codes: 76063.</t>
         </is>
       </c>
       <c r="C45" s="6" t="inlineStr">
@@ -1484,7 +1484,7 @@
       </c>
       <c r="B46" s="9" t="inlineStr">
         <is>
-          <t>(null - using code fallback)</t>
+          <t>FALLBACK: Professional heating and air conditioning services in North Richland Hills, Texas. Same-day HVAC repair, installation, and maintenance. Serving zip codes: 76148, 76180, 76182.</t>
         </is>
       </c>
       <c r="C46" s="6" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="B47" s="9" t="inlineStr">
         <is>
-          <t>(null - using code fallback)</t>
+          <t>FALLBACK: Professional heating and air conditioning services in Plano, Texas. Same-day HVAC repair, installation, and maintenance. Serving zip codes: 75023, 75024, 75025, 75075, 75093, 75252.</t>
         </is>
       </c>
       <c r="C47" s="6" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B48" s="9" t="inlineStr">
         <is>
-          <t>(null - using code fallback)</t>
+          <t>FALLBACK: Professional heating and air conditioning services in Richardson, Texas. Same-day HVAC repair, installation, and maintenance. Serving zip codes: 75080, 75081.</t>
         </is>
       </c>
       <c r="C48" s="6" t="inlineStr">
@@ -1550,7 +1550,7 @@
       </c>
       <c r="B49" s="9" t="inlineStr">
         <is>
-          <t>(null - using code fallback)</t>
+          <t>FALLBACK: Professional heating and air conditioning services in Roanoke, Texas. Same-day HVAC repair, installation, and maintenance. Serving zip codes: 76262.</t>
         </is>
       </c>
       <c r="C49" s="6" t="inlineStr">
@@ -1572,7 +1572,7 @@
       </c>
       <c r="B50" s="9" t="inlineStr">
         <is>
-          <t>(null - using code fallback)</t>
+          <t>FALLBACK: Professional heating and air conditioning services in Southlake, Texas. Same-day HVAC repair, installation, and maintenance. Serving zip codes: 76092.</t>
         </is>
       </c>
       <c r="C50" s="6" t="inlineStr">
@@ -1594,7 +1594,7 @@
       </c>
       <c r="B51" s="9" t="inlineStr">
         <is>
-          <t>(null - using code fallback)</t>
+          <t>FALLBACK: Professional heating and air conditioning services in The Colony, Texas. Same-day HVAC repair, installation, and maintenance. Serving zip codes: 75056.</t>
         </is>
       </c>
       <c r="C51" s="6" t="inlineStr">
@@ -1625,7 +1625,7 @@
     <row r="55">
       <c r="A55" s="12" t="inlineStr">
         <is>
-          <t>Red = No custom meta description set (using generic code fallback)</t>
+          <t>Red = Fallback code description (no custom meta description set in CMS)</t>
         </is>
       </c>
     </row>

--- a/frontend/public/DFW_HVAC_Site_Audit.xlsx
+++ b/frontend/public/DFW_HVAC_Site_Audit.xlsx
@@ -59,12 +59,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF3CD"/>
-        <bgColor rgb="00FFF3CD"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="00E0E0E0"/>
         <bgColor rgb="00E0E0E0"/>
       </patternFill>
@@ -73,6 +67,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="00F8D7DA"/>
         <bgColor rgb="00F8D7DA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF3CD"/>
+        <bgColor rgb="00FFF3CD"/>
       </patternFill>
     </fill>
   </fills>
@@ -122,7 +122,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -137,17 +137,14 @@
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
+      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -648,9 +645,9 @@
           <t>/faq</t>
         </is>
       </c>
-      <c r="B7" s="7" t="inlineStr">
-        <is>
-          <t>WARNING: "Test of the section. One Two Three"</t>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>Get answers to common HVAC questions — air conditioning, heating, heat pumps, preventative maintenance, and more. Expert advice from DFW HVAC, serving Dallas-Fort Worth for three generations.</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
@@ -807,7 +804,7 @@
           <t>N/A (307 redirects to /reviews)</t>
         </is>
       </c>
-      <c r="C14" s="8" t="inlineStr">
+      <c r="C14" s="7" t="inlineStr">
         <is>
           <t>Unpublished</t>
         </is>
@@ -834,9 +831,9 @@
           <t>/services/residential/air-conditioning</t>
         </is>
       </c>
-      <c r="B16" s="9" t="inlineStr">
-        <is>
-          <t>FALLBACK: Complete AC installation, repair, and replacement services for Dallas-Fort Worth homes.</t>
+      <c r="B16" s="8" t="inlineStr">
+        <is>
+          <t>Complete AC installation, repair, and replacement services for Dallas-Fort Worth homes.</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
@@ -856,9 +853,9 @@
           <t>/services/residential/heating</t>
         </is>
       </c>
-      <c r="B17" s="9" t="inlineStr">
-        <is>
-          <t>FALLBACK: Furnace repair, heat pump service, and heating system installation for DFW homes.</t>
+      <c r="B17" s="8" t="inlineStr">
+        <is>
+          <t>Furnace repair, heat pump service, and heating system installation for DFW homes.</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
@@ -878,9 +875,9 @@
           <t>/services/residential/preventative-maintenance</t>
         </is>
       </c>
-      <c r="B18" s="9" t="inlineStr">
-        <is>
-          <t>FALLBACK: Regular maintenance to keep your HVAC system running efficiently year-round.</t>
+      <c r="B18" s="8" t="inlineStr">
+        <is>
+          <t>Regular maintenance to keep your HVAC system running efficiently year-round.</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
@@ -900,9 +897,9 @@
           <t>/services/residential/indoor-air-quality</t>
         </is>
       </c>
-      <c r="B19" s="9" t="inlineStr">
-        <is>
-          <t>FALLBACK: Improve your home's air quality with our specialized solutions.</t>
+      <c r="B19" s="8" t="inlineStr">
+        <is>
+          <t>Improve your home's air quality with our specialized solutions.</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
@@ -922,9 +919,9 @@
           <t>/services/commercial/commercial-air-conditioning</t>
         </is>
       </c>
-      <c r="B20" s="9" t="inlineStr">
-        <is>
-          <t>FALLBACK: Large-scale AC systems for businesses and commercial properties in the DFW area.</t>
+      <c r="B20" s="8" t="inlineStr">
+        <is>
+          <t>Large-scale AC systems for businesses and commercial properties in the DFW area.</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
@@ -944,9 +941,9 @@
           <t>/services/commercial/commercial-heating</t>
         </is>
       </c>
-      <c r="B21" s="9" t="inlineStr">
-        <is>
-          <t>FALLBACK: Commercial heating solutions and repair to keep businesses and commercial properties comfortable.</t>
+      <c r="B21" s="8" t="inlineStr">
+        <is>
+          <t>Commercial heating solutions and repair to keep businesses and commercial properties comfortable.</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
@@ -966,9 +963,9 @@
           <t>/services/commercial/commercial-maintenance</t>
         </is>
       </c>
-      <c r="B22" s="9" t="inlineStr">
-        <is>
-          <t>FALLBACK: Comprehensive maintenance programs that help businesses keep their HVAC systems running efficiently and avoid downtime.</t>
+      <c r="B22" s="8" t="inlineStr">
+        <is>
+          <t>Comprehensive maintenance programs that help businesses keep their HVAC systems running efficiently and avoid downtime.</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
@@ -998,9 +995,9 @@
           <t>/cities-served/allen</t>
         </is>
       </c>
-      <c r="B24" s="9" t="inlineStr">
-        <is>
-          <t>FALLBACK: Professional heating and air conditioning services in Allen, Texas. Same-day HVAC repair, installation, and maintenance. Serving zip codes: 75013.</t>
+      <c r="B24" s="8" t="inlineStr">
+        <is>
+          <t>Professional heating and air conditioning services in Allen, Texas. Same-day HVAC repair, installation, and maintenance. Serving zip codes: 75013.</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
@@ -1020,9 +1017,9 @@
           <t>/cities-served/argyle</t>
         </is>
       </c>
-      <c r="B25" s="9" t="inlineStr">
-        <is>
-          <t>FALLBACK: Professional heating and air conditioning services in Argyle, Texas. Same-day HVAC repair, installation, and maintenance. Serving zip codes: 76226.</t>
+      <c r="B25" s="8" t="inlineStr">
+        <is>
+          <t>Professional heating and air conditioning services in Argyle, Texas. Same-day HVAC repair, installation, and maintenance. Serving zip codes: 76226.</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
@@ -1042,9 +1039,9 @@
           <t>/cities-served/arlington</t>
         </is>
       </c>
-      <c r="B26" s="9" t="inlineStr">
-        <is>
-          <t>FALLBACK: Professional heating and air conditioning services in Arlington, Texas. Same-day HVAC repair, installation, and maintenance. Serving zip codes: 76001, 76002, 76012, 76013, 76014, 76015, 76016, 76017, 76018.</t>
+      <c r="B26" s="8" t="inlineStr">
+        <is>
+          <t>Professional heating and air conditioning services in Arlington, Texas. Same-day HVAC repair, installation, and maintenance. Serving zip codes: 76001, 76002, 76012, 76013, 76014, 76015, 76016, 76017, 76018.</t>
         </is>
       </c>
       <c r="C26" s="6" t="inlineStr">
@@ -1064,9 +1061,9 @@
           <t>/cities-served/bedford</t>
         </is>
       </c>
-      <c r="B27" s="9" t="inlineStr">
-        <is>
-          <t>FALLBACK: Professional heating and air conditioning services in Bedford, Texas. Same-day HVAC repair, installation, and maintenance. Serving zip codes: 76021, 76022.</t>
+      <c r="B27" s="8" t="inlineStr">
+        <is>
+          <t>Professional heating and air conditioning services in Bedford, Texas. Same-day HVAC repair, installation, and maintenance. Serving zip codes: 76021, 76022.</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
@@ -1086,9 +1083,9 @@
           <t>/cities-served/carrollton</t>
         </is>
       </c>
-      <c r="B28" s="9" t="inlineStr">
-        <is>
-          <t>FALLBACK: Professional heating and air conditioning services in Carrollton, Texas. Same-day HVAC repair, installation, and maintenance. Serving zip codes: 75006, 75007, 75010.</t>
+      <c r="B28" s="8" t="inlineStr">
+        <is>
+          <t>Professional heating and air conditioning services in Carrollton, Texas. Same-day HVAC repair, installation, and maintenance. Serving zip codes: 75006, 75007, 75010.</t>
         </is>
       </c>
       <c r="C28" s="6" t="inlineStr">
@@ -1108,9 +1105,9 @@
           <t>/cities-served/colleyville</t>
         </is>
       </c>
-      <c r="B29" s="9" t="inlineStr">
-        <is>
-          <t>FALLBACK: Professional heating and air conditioning services in Colleyville, Texas. Same-day HVAC repair, installation, and maintenance. Serving zip codes: 76034.</t>
+      <c r="B29" s="8" t="inlineStr">
+        <is>
+          <t>Professional heating and air conditioning services in Colleyville, Texas. Same-day HVAC repair, installation, and maintenance. Serving zip codes: 76034.</t>
         </is>
       </c>
       <c r="C29" s="6" t="inlineStr">
@@ -1130,9 +1127,9 @@
           <t>/cities-served/coppell</t>
         </is>
       </c>
-      <c r="B30" s="9" t="inlineStr">
-        <is>
-          <t>FALLBACK: Professional heating and air conditioning services in Coppell, Texas. Same-day HVAC repair, installation, and maintenance. Serving zip codes: 75019.</t>
+      <c r="B30" s="8" t="inlineStr">
+        <is>
+          <t>Professional heating and air conditioning services in Coppell, Texas. Same-day HVAC repair, installation, and maintenance. Serving zip codes: 75019.</t>
         </is>
       </c>
       <c r="C30" s="6" t="inlineStr">
@@ -1152,9 +1149,9 @@
           <t>/cities-served/dallas</t>
         </is>
       </c>
-      <c r="B31" s="9" t="inlineStr">
-        <is>
-          <t>FALLBACK: Professional heating and air conditioning services in Dallas, Texas. Same-day HVAC repair, installation, and maintenance. Serving zip codes: 75201, 75202, 75204, 75205, 75206, 75207, 75208, 75209, 75214, 75218, 75219, 75225, 75229, 75230, 75238, 75244, 75248, 75254.</t>
+      <c r="B31" s="8" t="inlineStr">
+        <is>
+          <t>Professional heating and air conditioning services in Dallas, Texas. Same-day HVAC repair, installation, and maintenance. Serving zip codes: 75201, 75202, 75204, 75205, 75206, 75207, 75208, 75209, 75214, 75218, 75219, 75225, 75229, 75230, 75238, 75244, 75248, 75254.</t>
         </is>
       </c>
       <c r="C31" s="6" t="inlineStr">
@@ -1174,9 +1171,9 @@
           <t>/cities-served/denton</t>
         </is>
       </c>
-      <c r="B32" s="9" t="inlineStr">
-        <is>
-          <t>FALLBACK: Professional heating and air conditioning services in Denton, Texas. Same-day HVAC repair, installation, and maintenance. Serving zip codes: 76210.</t>
+      <c r="B32" s="8" t="inlineStr">
+        <is>
+          <t>Professional heating and air conditioning services in Denton, Texas. Same-day HVAC repair, installation, and maintenance. Serving zip codes: 76210.</t>
         </is>
       </c>
       <c r="C32" s="6" t="inlineStr">
@@ -1196,9 +1193,9 @@
           <t>/cities-served/euless</t>
         </is>
       </c>
-      <c r="B33" s="9" t="inlineStr">
-        <is>
-          <t>FALLBACK: Professional heating and air conditioning services in Euless, Texas. Same-day HVAC repair, installation, and maintenance. Serving zip codes: 76039, 76040.</t>
+      <c r="B33" s="8" t="inlineStr">
+        <is>
+          <t>Professional heating and air conditioning services in Euless, Texas. Same-day HVAC repair, installation, and maintenance. Serving zip codes: 76039, 76040.</t>
         </is>
       </c>
       <c r="C33" s="6" t="inlineStr">
@@ -1218,9 +1215,9 @@
           <t>/cities-served/farmers-branch</t>
         </is>
       </c>
-      <c r="B34" s="9" t="inlineStr">
-        <is>
-          <t>FALLBACK: Professional heating and air conditioning services in Farmers Branch, Texas. Same-day HVAC repair, installation, and maintenance. Serving zip codes: 75234.</t>
+      <c r="B34" s="8" t="inlineStr">
+        <is>
+          <t>Professional heating and air conditioning services in Farmers Branch, Texas. Same-day HVAC repair, installation, and maintenance. Serving zip codes: 75234.</t>
         </is>
       </c>
       <c r="C34" s="6" t="inlineStr">
@@ -1240,9 +1237,9 @@
           <t>/cities-served/flower-mound</t>
         </is>
       </c>
-      <c r="B35" s="9" t="inlineStr">
-        <is>
-          <t>FALLBACK: Professional heating and air conditioning services in Flower Mound, Texas. Same-day HVAC repair, installation, and maintenance. Serving zip codes: 75022, 75028, 75077.</t>
+      <c r="B35" s="8" t="inlineStr">
+        <is>
+          <t>Professional heating and air conditioning services in Flower Mound, Texas. Same-day HVAC repair, installation, and maintenance. Serving zip codes: 75022, 75028, 75077.</t>
         </is>
       </c>
       <c r="C35" s="6" t="inlineStr">
@@ -1262,9 +1259,9 @@
           <t>/cities-served/fort-worth</t>
         </is>
       </c>
-      <c r="B36" s="9" t="inlineStr">
-        <is>
-          <t>FALLBACK: Professional heating and air conditioning services in Fort Worth, Texas. Same-day HVAC repair, installation, and maintenance. Serving zip codes: 76118, 76120, 76137, 76177.</t>
+      <c r="B36" s="8" t="inlineStr">
+        <is>
+          <t>Professional heating and air conditioning services in Fort Worth, Texas. Same-day HVAC repair, installation, and maintenance. Serving zip codes: 76118, 76120, 76137, 76177.</t>
         </is>
       </c>
       <c r="C36" s="6" t="inlineStr">
@@ -1284,9 +1281,9 @@
           <t>/cities-served/frisco</t>
         </is>
       </c>
-      <c r="B37" s="9" t="inlineStr">
-        <is>
-          <t>FALLBACK: Professional heating and air conditioning services in Frisco, Texas. Same-day HVAC repair, installation, and maintenance. Serving zip codes: 75033, 75034, 75035, 75036.</t>
+      <c r="B37" s="8" t="inlineStr">
+        <is>
+          <t>Professional heating and air conditioning services in Frisco, Texas. Same-day HVAC repair, installation, and maintenance. Serving zip codes: 75033, 75034, 75035, 75036.</t>
         </is>
       </c>
       <c r="C37" s="6" t="inlineStr">
@@ -1306,9 +1303,9 @@
           <t>/cities-served/grapevine</t>
         </is>
       </c>
-      <c r="B38" s="9" t="inlineStr">
-        <is>
-          <t>FALLBACK: Professional heating and air conditioning services in Grapevine, Texas. Same-day HVAC repair, installation, and maintenance. Serving zip codes: 76051.</t>
+      <c r="B38" s="8" t="inlineStr">
+        <is>
+          <t>Professional heating and air conditioning services in Grapevine, Texas. Same-day HVAC repair, installation, and maintenance. Serving zip codes: 76051.</t>
         </is>
       </c>
       <c r="C38" s="6" t="inlineStr">
@@ -1328,9 +1325,9 @@
           <t>/cities-served/haslet</t>
         </is>
       </c>
-      <c r="B39" s="9" t="inlineStr">
-        <is>
-          <t>FALLBACK: Professional heating and air conditioning services in Haslet, Texas. Same-day HVAC repair, installation, and maintenance. Serving zip codes: 76052.</t>
+      <c r="B39" s="8" t="inlineStr">
+        <is>
+          <t>Professional heating and air conditioning services in Haslet, Texas. Same-day HVAC repair, installation, and maintenance. Serving zip codes: 76052.</t>
         </is>
       </c>
       <c r="C39" s="6" t="inlineStr">
@@ -1350,9 +1347,9 @@
           <t>/cities-served/hurst</t>
         </is>
       </c>
-      <c r="B40" s="9" t="inlineStr">
-        <is>
-          <t>FALLBACK: Professional heating and air conditioning services in Hurst, Texas. Same-day HVAC repair, installation, and maintenance. Serving zip codes: 76054.</t>
+      <c r="B40" s="8" t="inlineStr">
+        <is>
+          <t>Professional heating and air conditioning services in Hurst, Texas. Same-day HVAC repair, installation, and maintenance. Serving zip codes: 76054.</t>
         </is>
       </c>
       <c r="C40" s="6" t="inlineStr">
@@ -1372,9 +1369,9 @@
           <t>/cities-served/irving</t>
         </is>
       </c>
-      <c r="B41" s="9" t="inlineStr">
-        <is>
-          <t>FALLBACK: Professional heating and air conditioning services in Irving, Texas. Same-day HVAC repair, installation, and maintenance. Serving zip codes: 75038, 75039, 75062, 75063.</t>
+      <c r="B41" s="8" t="inlineStr">
+        <is>
+          <t>Professional heating and air conditioning services in Irving, Texas. Same-day HVAC repair, installation, and maintenance. Serving zip codes: 75038, 75039, 75062, 75063.</t>
         </is>
       </c>
       <c r="C41" s="6" t="inlineStr">
@@ -1394,9 +1391,9 @@
           <t>/cities-served/keller</t>
         </is>
       </c>
-      <c r="B42" s="9" t="inlineStr">
-        <is>
-          <t>FALLBACK: Professional heating and air conditioning services in Keller, Texas. Same-day HVAC repair, installation, and maintenance. Serving zip codes: 76244, 76248.</t>
+      <c r="B42" s="8" t="inlineStr">
+        <is>
+          <t>Professional heating and air conditioning services in Keller, Texas. Same-day HVAC repair, installation, and maintenance. Serving zip codes: 76244, 76248.</t>
         </is>
       </c>
       <c r="C42" s="6" t="inlineStr">
@@ -1416,9 +1413,9 @@
           <t>/cities-served/lake-dallas</t>
         </is>
       </c>
-      <c r="B43" s="9" t="inlineStr">
-        <is>
-          <t>FALLBACK: Professional heating and air conditioning services in Lake Dallas, Texas. Same-day HVAC repair, installation, and maintenance. Serving zip codes: 75065.</t>
+      <c r="B43" s="8" t="inlineStr">
+        <is>
+          <t>Professional heating and air conditioning services in Lake Dallas, Texas. Same-day HVAC repair, installation, and maintenance. Serving zip codes: 75065.</t>
         </is>
       </c>
       <c r="C43" s="6" t="inlineStr">
@@ -1438,9 +1435,9 @@
           <t>/cities-served/lewisville</t>
         </is>
       </c>
-      <c r="B44" s="9" t="inlineStr">
-        <is>
-          <t>FALLBACK: Professional heating and air conditioning services in Lewisville, Texas. Same-day HVAC repair, installation, and maintenance. Serving zip codes: 75057, 75067.</t>
+      <c r="B44" s="8" t="inlineStr">
+        <is>
+          <t>Professional heating and air conditioning services in Lewisville, Texas. Same-day HVAC repair, installation, and maintenance. Serving zip codes: 75057, 75067.</t>
         </is>
       </c>
       <c r="C44" s="6" t="inlineStr">
@@ -1460,9 +1457,9 @@
           <t>/cities-served/mansfield</t>
         </is>
       </c>
-      <c r="B45" s="9" t="inlineStr">
-        <is>
-          <t>FALLBACK: Professional heating and air conditioning services in Mansfield, Texas. Same-day HVAC repair, installation, and maintenance. Serving zip codes: 76063.</t>
+      <c r="B45" s="8" t="inlineStr">
+        <is>
+          <t>Professional heating and air conditioning services in Mansfield, Texas. Same-day HVAC repair, installation, and maintenance. Serving zip codes: 76063.</t>
         </is>
       </c>
       <c r="C45" s="6" t="inlineStr">
@@ -1482,9 +1479,9 @@
           <t>/cities-served/north-richland-hills</t>
         </is>
       </c>
-      <c r="B46" s="9" t="inlineStr">
-        <is>
-          <t>FALLBACK: Professional heating and air conditioning services in North Richland Hills, Texas. Same-day HVAC repair, installation, and maintenance. Serving zip codes: 76148, 76180, 76182.</t>
+      <c r="B46" s="8" t="inlineStr">
+        <is>
+          <t>Professional heating and air conditioning services in North Richland Hills, Texas. Same-day HVAC repair, installation, and maintenance. Serving zip codes: 76148, 76180, 76182.</t>
         </is>
       </c>
       <c r="C46" s="6" t="inlineStr">
@@ -1504,9 +1501,9 @@
           <t>/cities-served/plano</t>
         </is>
       </c>
-      <c r="B47" s="9" t="inlineStr">
-        <is>
-          <t>FALLBACK: Professional heating and air conditioning services in Plano, Texas. Same-day HVAC repair, installation, and maintenance. Serving zip codes: 75023, 75024, 75025, 75075, 75093, 75252.</t>
+      <c r="B47" s="8" t="inlineStr">
+        <is>
+          <t>Professional heating and air conditioning services in Plano, Texas. Same-day HVAC repair, installation, and maintenance. Serving zip codes: 75023, 75024, 75025, 75075, 75093, 75252.</t>
         </is>
       </c>
       <c r="C47" s="6" t="inlineStr">
@@ -1526,9 +1523,9 @@
           <t>/cities-served/richardson</t>
         </is>
       </c>
-      <c r="B48" s="9" t="inlineStr">
-        <is>
-          <t>FALLBACK: Professional heating and air conditioning services in Richardson, Texas. Same-day HVAC repair, installation, and maintenance. Serving zip codes: 75080, 75081.</t>
+      <c r="B48" s="8" t="inlineStr">
+        <is>
+          <t>Professional heating and air conditioning services in Richardson, Texas. Same-day HVAC repair, installation, and maintenance. Serving zip codes: 75080, 75081.</t>
         </is>
       </c>
       <c r="C48" s="6" t="inlineStr">
@@ -1548,9 +1545,9 @@
           <t>/cities-served/roanoke</t>
         </is>
       </c>
-      <c r="B49" s="9" t="inlineStr">
-        <is>
-          <t>FALLBACK: Professional heating and air conditioning services in Roanoke, Texas. Same-day HVAC repair, installation, and maintenance. Serving zip codes: 76262.</t>
+      <c r="B49" s="8" t="inlineStr">
+        <is>
+          <t>Professional heating and air conditioning services in Roanoke, Texas. Same-day HVAC repair, installation, and maintenance. Serving zip codes: 76262.</t>
         </is>
       </c>
       <c r="C49" s="6" t="inlineStr">
@@ -1570,9 +1567,9 @@
           <t>/cities-served/southlake</t>
         </is>
       </c>
-      <c r="B50" s="9" t="inlineStr">
-        <is>
-          <t>FALLBACK: Professional heating and air conditioning services in Southlake, Texas. Same-day HVAC repair, installation, and maintenance. Serving zip codes: 76092.</t>
+      <c r="B50" s="8" t="inlineStr">
+        <is>
+          <t>Professional heating and air conditioning services in Southlake, Texas. Same-day HVAC repair, installation, and maintenance. Serving zip codes: 76092.</t>
         </is>
       </c>
       <c r="C50" s="6" t="inlineStr">
@@ -1592,9 +1589,9 @@
           <t>/cities-served/the-colony</t>
         </is>
       </c>
-      <c r="B51" s="9" t="inlineStr">
-        <is>
-          <t>FALLBACK: Professional heating and air conditioning services in The Colony, Texas. Same-day HVAC repair, installation, and maintenance. Serving zip codes: 75056.</t>
+      <c r="B51" s="8" t="inlineStr">
+        <is>
+          <t>Professional heating and air conditioning services in The Colony, Texas. Same-day HVAC repair, installation, and maintenance. Serving zip codes: 75056.</t>
         </is>
       </c>
       <c r="C51" s="6" t="inlineStr">
@@ -1609,21 +1606,21 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="10" t="inlineStr">
+      <c r="A53" s="9" t="inlineStr">
         <is>
           <t>Legend:</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="11" t="inlineStr">
+      <c r="A54" s="10" t="inlineStr">
         <is>
           <t>Yellow = Needs immediate fix (test/incorrect data)</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="12" t="inlineStr">
+      <c r="A55" s="11" t="inlineStr">
         <is>
           <t>Red = Fallback code description (no custom meta description set in CMS)</t>
         </is>

--- a/frontend/public/DFW_HVAC_Site_Audit.xlsx
+++ b/frontend/public/DFW_HVAC_Site_Audit.xlsx
@@ -669,7 +669,7 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>Read 130+ 5-star reviews from real DFW HVAC customers. Family-owned HVAC contractor serving Dallas-Fort Worth since 1974. See why customers trust us.</t>
+          <t>Read 145+ 5-star reviews from real DFW HVAC customers. Three generations of trusted HVAC service in Dallas-Fort Worth. See why customers trust us.</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
